--- a/war-room-concorrencia/contexto-e-apoio/arquivos-finais/relatorio-keywords.xlsx
+++ b/war-room-concorrencia/contexto-e-apoio/arquivos-finais/relatorio-keywords.xlsx
@@ -7,10 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="⚠ AVISO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Keywords" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leilão por Campanha" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Metodologia" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Keywords" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leilão por Campanha" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metodologia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,11 +36,6 @@
       <b val="1"/>
       <color rgb="001F2A44"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B00020"/>
-      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
@@ -69,16 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -448,51 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>⚠ ESTE RELATÓRIO USA DADO SIMULADO, NÃO REAL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>A conta Google Ads da Joie ainda não está conectada no Windsor.ai desta integração (get_connectors só mostra a GA4 — ver references/fontes-e-limitacoes.md, achado de 2026-08-01). Os números de keyword/leilão abaixo (impression share, CPC, Quality Score, domínios concorrentes) servem só para mostrar o FORMATO do relatório — não são dado real da conta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Assim que o Google Ads estiver conectado (get_connectors mostrando accounts para google_ads), rode gerar_relatorio_keywords.py com os JSONs reais puxados via Windsor.ai (ver aba Metodologia) para substituir por dado medido de verdade.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -510,62 +457,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CAMPANHA</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>KEYWORD</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>IMPRESSIONS</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CLICKS</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CTR_%</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CPC_MEDIO</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>QUALITY_SCORE</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>IMPRESSION_SHARE</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>RANK_LOST_IMPRESSION_SHARE</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>FIRST_PAGE_CPC</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TOP_OF_PAGE_CPC</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>DOMINIOS_NO_LEILAO</t>
         </is>
@@ -574,34 +521,34 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Brand.</t>
+          <t>Pmax - Todos os Produtos.</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>joie suplementos</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5200</v>
+        <v>143291</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>890</v>
+        <v>3309</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>17.1</v>
+        <v>2.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.35</v>
+        <v>1.15</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>97</v>
+        <v>12.2</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -622,34 +569,36 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Brand.</t>
+          <t>Geração de demanda - Capitais</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>joie</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3100</v>
+        <v>112698</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>540</v>
+        <v>3932</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17.4</v>
+        <v>3.5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>94.5</v>
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -670,34 +619,34 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Search.</t>
+          <t>Shopping - Colageno</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>suplementos alimentares</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2100</v>
+        <v>74061</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>75</v>
+        <v>1292</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1.05</v>
+        <v>0.34</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>50</v>
+        <v>32.7</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -711,41 +660,41 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+          <t>(nenhum capturado)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Search.</t>
+          <t>Pmax - Amaze.</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>whey protein</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1450</v>
+        <v>46920</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>62</v>
+        <v>1251</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46</v>
+        <v>74.7</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -759,41 +708,41 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+          <t>(nenhum capturado)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Search - Linha Joie Fit</t>
+          <t>Pmax - Linha Joie Fit</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>whey protein isolado</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1320</v>
+        <v>43658</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>58</v>
+        <v>965</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1.15</v>
+        <v>1.78</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>22</v>
+        <v>13.9</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -807,41 +756,41 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>gsuplementos.com.br (1x), vitafor.com.br (1x)</t>
+          <t>(nenhum capturado)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Search.</t>
+          <t>Pmax - Faciderm.</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>omega 3</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>980</v>
+        <v>34358</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>40</v>
+        <v>2219</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>40</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -855,41 +804,41 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+          <t>(nenhum capturado)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Search.</t>
+          <t>Search - Linha Joie Fit</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>polivitamínico</t>
+          <t>whey protein</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>860</v>
+        <v>4436</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.89</v>
+        <v>2.43</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>42</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -903,55 +852,1769 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>omega 3</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2355</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Joie</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2291</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>532</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), shopee.com.br (29x), vhita.com.br (27x), magazineluiza.com.br (17x), puravida.com.br (14x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>magnésio</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1347</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>suplementos alimentares</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1173</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Joie suplementos</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>424</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), shopee.com.br (29x), vhita.com.br (27x), magazineluiza.com.br (17x), puravida.com.br (14x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Search - Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>creatina monohidratada</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>640</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G9" s="2" t="n">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Colageno</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>823</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>polivitaminico</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>461</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>magnésio quelato</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>vitamina D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>whey protein sabor chocolate</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="D18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="I9" s="2" t="n">
+      <c r="E18" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>magnésio quelato para que serve</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>colageno verisol</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>suplementos vitamínicos</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>colageno</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>N/D (não estimado pelo Google)</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>N/D (não estimado pelo Google)</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>gsuplementos.com.br (1x), vitafor.com.br (1x)</t>
+      <c r="D22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>suplemento de proteina e colageno verisol</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>whey protein</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>whey com colageno</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Ômega 3</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>suplemento para memoria</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Colageno verisol</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>vitamina d3</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>colágeno verisol</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>suplemento para menopausa</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>suplemento para emagrecimento</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>vitamina d3 para que serve</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>cálcio</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>vitamina para os ossos</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>multivitamínico</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>suplementos para memoria</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>cartamo</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>polivitamínico</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>coezima q10</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>testofen</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>colageno hidrolisado verisol em po</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>N/D (não estimado pelo Google)</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
         </is>
       </c>
     </row>
@@ -960,13 +2623,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -975,17 +2638,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CAMPANHA</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>DOMINIO_CONCORRENTE</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>APARICOES_NO_PERIODO</t>
         </is>
@@ -994,60 +2657,1215 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Search - Linha Joie Fit</t>
+          <t>Brand.</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>gsuplementos.com.br</t>
+          <t>mercadolivre.com.br</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Search - Linha Joie Fit</t>
+          <t>Brand.</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>vitafor.com.br</t>
+          <t>shopee.com.br</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Search.</t>
+          <t>Brand.</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>maxtitanium.com.br</t>
+          <t>vhita.com.br</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Search.</t>
+          <t>Brand.</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>magazineluiza.com.br</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>puravida.com.br</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>encapsnow.com.br</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>amazon.com.br</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>weonnutrition.com.br</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>vitafor.com.br</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>amaramar.com.br</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>yogi.baby</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>lauton.com.br</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>drogaraia.com.br</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>fitoessencia.com.br</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>nacionalsuplementos.com.br</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>natusvita.com.br</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>oficialfarma.com.br</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>toptherm.com.br</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>clubemonster.com.br</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>desejoenatureza.com.br</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>mantecorpsaude.com.br</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>nestlenutre.com.br</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>nestlevital.com.br</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>sede.energy</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>vivatrue.com.br</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>google.com</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>biostevi.com.br</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>mercadolivre.com.br</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C30" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>puravida.com.br</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>shopee.com.br</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>vitafor.com.br</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>renovabe.com.br</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>soldiersnutrition.com.br</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>darklabsuplementos.com.br</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>amazon.com.br</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>wpinkslvsuplementos.com.br</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>coompare.com.br</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>vivatrue.com.br</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>sanavita.com.br</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>duxhumanhealth.com</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>netshoes.com.br</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>fixaderme.com.br</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>vhita.com.br</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>encapsnow.com.br</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>casadossuplementos.com</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>souemana.com.br</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>paceit.com.br</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>rejuv.com.br</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>amaramar.com.br</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>magazineluiza.com.br</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>bigens.com.br</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>creatineforhealth.com</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>myfithealthy.com.br</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>essentialnutrition.com.br</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>adaptogen.com.br</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>my-best.com</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>oficialfarma.com.br</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>vitascience.com</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>puravida.com.br</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>shopee.com.br</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>vhita.com.br</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>vitafor.com.br</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>biostevi.com.br</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>oficialfarma.com.br</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>natusvita.com.br</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>amazon.com.br</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>fitoessencia.com.br</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>sanavita.com.br</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>renovabe.com.br</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>alwaysfit.com.br</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>drogariaspacheco.com.br</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>gfarma.com</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>emporioterranativa.com.br</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>alobela.com.br</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>elevesuplementos.com.br</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>oceandrop.com.br</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1056,7 +3874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1070,7 +3888,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Fonte</t>
         </is>
@@ -1109,7 +3927,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SIMULADO — ver aviso abaixo.</t>
+          <t>REAL — puxado ao vivo da conta Google Ads via Windsor.ai.</t>
         </is>
       </c>
     </row>
